--- a/01_data/02_output_data/02_unidirectional_results/02_paper_ESR/02_prepared_results/output_2019_prepared.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/02_paper_ESR/02_prepared_results/output_2019_prepared.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\hydrogen_grid\01_data\02_output_data\02_unidirectional_results\02_paper_ESR\02_prepared_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CAD7F4-CC65-49FA-B97B-1BB98B0FF3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BC6AB9-1F1F-4FC4-81FA-2DD3F2C1B85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="386">
   <si>
     <t>Commodity</t>
   </si>
@@ -1196,6 +1196,9 @@
   </si>
   <si>
     <t>LNG</t>
+  </si>
+  <si>
+    <t>sum to Europe BP (adjusted)</t>
   </si>
 </sst>
 </file>
@@ -1335,8 +1338,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1377,40 +1380,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1458,16 +1427,50 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thick">
           <color theme="0"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
           <color theme="0"/>
-        </bottom>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2565,10 +2568,10 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{237B7A63-4090-4979-9020-465A08604C11}" name="Table10" displayName="Table10" ref="A1:B5" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{237B7A63-4090-4979-9020-465A08604C11}" name="Table10" displayName="Table10" ref="A1:B5" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A1:B5" xr:uid="{237B7A63-4090-4979-9020-465A08604C11}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00752DC9-E593-487E-A5D1-13C787C04187}" name="Source" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00752DC9-E593-487E-A5D1-13C787C04187}" name="Source" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{6629D851-BA10-4FF7-87DE-B4C77A908AD3}" name="Flow (GWh)" dataDxfId="0">
       <calculatedColumnFormula>Russian_Supply_Europe!E2</calculatedColumnFormula>
     </tableColumn>
@@ -2593,8 +2596,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3417075B-B51B-429B-8BA8-43E190BF8519}" name="Table2" displayName="Table2" ref="A1:C14" totalsRowShown="0">
-  <autoFilter ref="A1:C14" xr:uid="{3417075B-B51B-429B-8BA8-43E190BF8519}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3417075B-B51B-429B-8BA8-43E190BF8519}" name="Table2" displayName="Table2" ref="A1:C13" totalsRowShown="0">
+  <autoFilter ref="A1:C13" xr:uid="{3417075B-B51B-429B-8BA8-43E190BF8519}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A239A1DC-0210-4956-ABE7-EF6CDA5A30E2}" name="Edge"/>
     <tableColumn id="2" xr3:uid="{322E7DE0-B95E-46AC-9403-C71D0E63B73A}" name="Flow (GWh)" dataDxfId="15">
@@ -9723,6 +9726,7 @@
     <col min="6" max="6" width="19.5546875" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -9756,11 +9760,11 @@
       </c>
       <c r="G2" s="5">
         <f>SUM(Table2[Flow (GWh)])</f>
-        <v>1040847.0036351338</v>
+        <v>752115.36298513378</v>
       </c>
       <c r="H2" s="5">
-        <f>(G3-G2)</f>
-        <v>129598.99636486615</v>
+        <f>(G2-G3)</f>
+        <v>-11898.637014866224</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -9776,19 +9780,19 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>385</v>
       </c>
       <c r="G3" s="5">
-        <f>119.8*9.77*1000</f>
-        <v>1170446</v>
+        <f>119.8*9.77*1000-Russian_Supply_Europe!E6-Africa_Supply_Europe!E6-Norway_Supply_Europe!E6</f>
+        <v>764014</v>
       </c>
       <c r="H3">
         <f>H2/G3</f>
-        <v>0.11072616452605771</v>
+        <v>-1.5573846833783444E-2</v>
       </c>
       <c r="I3" s="8">
         <f>H3*100</f>
-        <v>11.072616452605772</v>
+        <v>-1.5573846833783445</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -9803,6 +9807,21 @@
         <f>VLOOKUP(LNG_Import_use!$A4,Raw!$C$3:$E$357,3,FALSE)</f>
         <v>0</v>
       </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="5">
+        <f>119.8*9.77*1000</f>
+        <v>1170446</v>
+      </c>
+      <c r="H4" s="5">
+        <f>(G2-G4)/G4</f>
+        <v>-0.35741130903507401</v>
+      </c>
+      <c r="I4" s="8">
+        <f>H4*100</f>
+        <v>-35.741130903507404</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -9829,6 +9848,9 @@
         <f>VLOOKUP(LNG_Import_use!$A6,Raw!$C$3:$E$357,3,FALSE)</f>
         <v>0.1926213134118839</v>
       </c>
+      <c r="G6">
+        <v>752115.36298513401</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -9842,6 +9864,9 @@
         <f>VLOOKUP(LNG_Import_use!$A7,Raw!$C$3:$E$357,3,FALSE)</f>
         <v>0</v>
       </c>
+      <c r="G7">
+        <v>764014</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -9855,6 +9880,9 @@
         <f>VLOOKUP(LNG_Import_use!$A8,Raw!$C$3:$E$357,3,FALSE)</f>
         <v>0</v>
       </c>
+      <c r="G8">
+        <v>1170446</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -9922,17 +9950,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5">
-        <f>VLOOKUP(LNG_Import_use!$A14,Raw!$C$3:$E$357,2,FALSE)</f>
-        <v>288731.64065000002</v>
-      </c>
-      <c r="C14" s="5">
-        <f>VLOOKUP(LNG_Import_use!$A14,Raw!$C$3:$E$357,3,FALSE)</f>
-        <v>0.67781835578394822</v>
-      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10165,7 +10184,7 @@
     <col min="3" max="3" width="19.77734375" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -10194,8 +10213,8 @@
         <v>1921897.2182650445</v>
       </c>
       <c r="F2" s="5">
-        <f>(E3-E2)</f>
-        <v>-85137.218265044503</v>
+        <f>(E2-E3)</f>
+        <v>-115147.7817349555</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -10209,16 +10228,16 @@
         <v>65</v>
       </c>
       <c r="E3" s="5">
-        <f>188*9.77*1000</f>
-        <v>1836760</v>
+        <f>188*9.77*1000+E6</f>
+        <v>2037045</v>
       </c>
       <c r="F3">
         <f>F2/E3</f>
-        <v>-4.635184687441174E-2</v>
+        <v>-5.6526871883024431E-2</v>
       </c>
       <c r="G3" s="8">
         <f>F3*100</f>
-        <v>-4.635184687441174</v>
+        <v>-5.6526871883024432</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -10244,6 +10263,10 @@
       </c>
       <c r="B6" s="5">
         <v>354643.73091044102</v>
+      </c>
+      <c r="E6">
+        <f>20.5*9.77*1000</f>
+        <v>200285</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -10478,8 +10501,8 @@
         <v>417068.39837955032</v>
       </c>
       <c r="F2" s="5">
-        <f>(E3-E2)</f>
-        <v>-8682.3983795503736</v>
+        <f>(E2-E3)</f>
+        <v>8682.3983795503154</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -10493,16 +10516,16 @@
         <v>65</v>
       </c>
       <c r="E3" s="5">
-        <f>41.8*9.77*1000</f>
-        <v>408385.99999999994</v>
+        <f>26.6*9.77*1000+E6</f>
+        <v>408386</v>
       </c>
       <c r="F3">
         <f>F2/E3</f>
-        <v>-2.1260274298213883E-2</v>
+        <v>2.1260274298213738E-2</v>
       </c>
       <c r="G3" s="8">
         <f>F3*100</f>
-        <v>-2.1260274298213884</v>
+        <v>2.1260274298213737</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -10524,6 +10547,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
+      <c r="E6">
+        <f>15.2*9.77*1000</f>
+        <v>148504</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
@@ -10585,8 +10612,8 @@
         <v>1118079.4555095769</v>
       </c>
       <c r="F2" s="5">
-        <f>(E3-E2)</f>
-        <v>-52172.455509576946</v>
+        <f>(E2-E3)</f>
+        <v>-5470.5444904230535</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -10600,16 +10627,16 @@
         <v>65</v>
       </c>
       <c r="E3" s="5">
-        <f>109.1*9.77*1000</f>
-        <v>1065907</v>
+        <f>109.1*9.77*1000+E6</f>
+        <v>1123550</v>
       </c>
       <c r="F3">
         <f>F2/E3</f>
-        <v>-4.8946536151443745E-2</v>
+        <v>-4.8689817902390223E-3</v>
       </c>
       <c r="G3" s="8">
         <f>F3*100</f>
-        <v>-4.8946536151443745</v>
+        <v>-0.48689817902390226</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -10635,6 +10662,10 @@
       </c>
       <c r="B6" s="5">
         <v>397158.93150692643</v>
+      </c>
+      <c r="E6">
+        <f>5.9*9.77*1000</f>
+        <v>57643</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -10702,8 +10733,8 @@
         <v>73260</v>
       </c>
       <c r="F2" s="5">
-        <f>(E3-E2)</f>
-        <v>36163.999999999985</v>
+        <f>(E2-E3)</f>
+        <v>-36163.999999999985</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -10722,11 +10753,11 @@
       </c>
       <c r="F3">
         <f>F2/E3</f>
-        <v>0.33049422430179842</v>
+        <v>-0.33049422430179842</v>
       </c>
       <c r="G3" s="8">
         <f>F3*100</f>
-        <v>33.049422430179845</v>
+        <v>-33.049422430179845</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -10779,6 +10810,7 @@
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
     <col min="6" max="6" width="16.77734375" customWidth="1"/>
     <col min="7" max="7" width="12.21875" customWidth="1"/>
   </cols>
@@ -10810,8 +10842,8 @@
         <v>3530305.0721541718</v>
       </c>
       <c r="G2" s="5">
-        <f>(F3-F2)</f>
-        <v>-183103.07215417176</v>
+        <f>(F2-F3)</f>
+        <v>183103.07215417176</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -10823,7 +10855,7 @@
         <v>417068.39837955032</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>385</v>
       </c>
       <c r="F3" s="5">
         <f>(471.3-38.2-90.5)*9.77*1000</f>
@@ -10831,11 +10863,11 @@
       </c>
       <c r="G3">
         <f>G2/F3</f>
-        <v>-5.4703323000575337E-2</v>
+        <v>5.4703323000575337E-2</v>
       </c>
       <c r="H3" s="8">
         <f>G3*100</f>
-        <v>-5.4703323000575335</v>
+        <v>5.4703323000575335</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -10846,6 +10878,21 @@
         <f>Norway_Supply_Europe!E2</f>
         <v>1118079.4555095769</v>
       </c>
+      <c r="E4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5">
+        <f>F3-Norway_Supply_Europe!E6-Africa_Supply_Europe!E6-Russian_Supply_Europe!E6</f>
+        <v>2940770</v>
+      </c>
+      <c r="G4" s="5">
+        <f>(F2-F4)/F4</f>
+        <v>0.20046962943520635</v>
+      </c>
+      <c r="H4" s="8">
+        <f>G4*100</f>
+        <v>20.046962943520636</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
@@ -10867,18 +10914,18 @@
       </c>
       <c r="B7" s="5">
         <f>LNG_Import_use!G2</f>
-        <v>1040847.0036351338</v>
+        <v>752115.36298513378</v>
       </c>
       <c r="E7" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="5">
         <f>F2+B7</f>
-        <v>4571152.0757893054</v>
+        <v>4282420.4351393059</v>
       </c>
       <c r="G7" s="5">
-        <f>(F8-F7)</f>
-        <v>-53504.075789305381</v>
+        <f>(F7-F8)</f>
+        <v>-235227.56486069411</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -10886,16 +10933,16 @@
         <v>65</v>
       </c>
       <c r="F8" s="5">
-        <f>F3+LNG_Import_use!G3</f>
+        <f>F3+LNG_Import_use!G4</f>
         <v>4517648</v>
       </c>
       <c r="G8">
         <f>G7/F8</f>
-        <v>-1.1843347642247776E-2</v>
+        <v>-5.2068590749145154E-2</v>
       </c>
       <c r="H8" s="8">
         <f>G8*100</f>
-        <v>-1.1843347642247777</v>
+        <v>-5.2068590749145152</v>
       </c>
     </row>
   </sheetData>
